--- a/response_save_audit.xlsx
+++ b/response_save_audit.xlsx
@@ -413,82 +413,618 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:CS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>saved_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>response_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>profile_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>response_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>submitted_at</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>participant_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>investigator_username</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>study_date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>study_datetime</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>height_cms</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>weight_kgs</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>mobile_no</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>school_anganwadi_name</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>location_type</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>investigator_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>saved_at</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>child_id_code</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>dob</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>age_full</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>age_calculated_at</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>age_completed</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>birth_order</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>siblings_count</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>family_type</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>family_members_total</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>religion</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>religion_other</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>social_category</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>edu_head_family</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>occupation_head_family</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>monthly_income</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>kuppuswamy_total_score</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ses_class</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>low_birth_weight</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>chronic_illness</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>chronic_illness_specify</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>worm_infestation</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>deworming_tablet</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>iron_supplementation</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>diet_type</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>freq_green_leafy</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>freq_jaggery</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>freq_dates</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>freq_eggs</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>freq_meat</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>freq_fruits</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>hb_previously_tested</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>prev_hb_result</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>prev_hb_device</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>prev_hb_device_other</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>device_seq_1</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>device_seq_2</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>device_seq_3</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>masimo_start_time</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>masimo_reading</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>masimo_attempts</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>masimo_end_time</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>masimo_flacc_face</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>masimo_flacc_legs</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>masimo_flacc_activity</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>masimo_flacc_cry</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>masimo_flacc_consolability</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>masimo_flacc_total</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>poc_start_time</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>poc_hb_value</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>poc_attempts</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>poc_end_time</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>poc_flacc_face</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>poc_flacc_legs</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>poc_flacc_activity</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>poc_flacc_cry</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>poc_flacc_consolability</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>poc_flacc_total</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>lab_start_time</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>lab_hb_value</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>lab_attempts</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>lab_end_time</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>lab_flacc_face</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>lab_flacc_legs</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>lab_flacc_activity</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>lab_flacc_cry</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>lab_flacc_consolability</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>lab_flacc_total</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>parent_q_39</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>parent_q_40</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>parent_q_41</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>parent_q_42</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>parent_q_43</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>parent_q_44</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>parent_q_45</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>parent_q_46</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>child_classification</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>ifa_dose</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>referral_advised</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>referral_destination</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>referral_other</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>investigator_signature</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>referral_date</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-04-02 10:50:09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>789616cd-6e2a-4d55-af36-759f824bbdcb</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>PR150722MDOH</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>789616cd-6e2a-4d55-af36-759f824bbdcb</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:50:08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Praneeth reddy</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Jahnavi</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Jahnavi</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-04-02 10:50:09</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-04-02 10:50:08</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
